--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1250"/>
+  <dimension ref="A1:B1251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12930,6 +12930,16 @@
         <v>51.9</v>
       </c>
     </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B1251" t="n">
+        <v>52.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1251"/>
+  <dimension ref="A1:B1252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12940,6 +12940,16 @@
         <v>52.14</v>
       </c>
     </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B1252" t="n">
+        <v>52.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1252"/>
+  <dimension ref="A1:B1253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12950,6 +12950,16 @@
         <v>52.29</v>
       </c>
     </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B1253" t="n">
+        <v>52.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1253"/>
+  <dimension ref="A1:B1254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12960,6 +12960,16 @@
         <v>52.46</v>
       </c>
     </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="B1254" t="n">
+        <v>52.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1255"/>
+  <dimension ref="A1:B1256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12980,6 +12980,16 @@
         <v>52.53</v>
       </c>
     </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B1256" t="n">
+        <v>52.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1256"/>
+  <dimension ref="A1:B1257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12990,6 +12990,16 @@
         <v>52.33</v>
       </c>
     </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B1257" t="n">
+        <v>52.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1257"/>
+  <dimension ref="A1:B1258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13000,6 +13000,16 @@
         <v>52.4</v>
       </c>
     </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B1258" t="n">
+        <v>52.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1258"/>
+  <dimension ref="A1:B1259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13010,6 +13010,16 @@
         <v>52.44</v>
       </c>
     </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B1259" t="n">
+        <v>52.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1261"/>
+  <dimension ref="A1:B1262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13040,6 +13040,16 @@
         <v>52.36</v>
       </c>
     </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B1262" t="n">
+        <v>52.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1263"/>
+  <dimension ref="A1:B1264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13060,6 +13060,16 @@
         <v>52.12</v>
       </c>
     </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B1264" t="n">
+        <v>52.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1264"/>
+  <dimension ref="A1:B1265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13070,6 +13070,16 @@
         <v>52.06</v>
       </c>
     </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B1265" t="n">
+        <v>52.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1265"/>
+  <dimension ref="A1:B1266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13080,6 +13080,16 @@
         <v>52.01</v>
       </c>
     </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B1266" t="n">
+        <v>51.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1266"/>
+  <dimension ref="A1:B1267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13090,6 +13090,16 @@
         <v>51.79</v>
       </c>
     </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B1267" t="n">
+        <v>51.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1268"/>
+  <dimension ref="A1:B1269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13110,6 +13110,16 @@
         <v>52.09</v>
       </c>
     </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B1269" t="n">
+        <v>52.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1270"/>
+  <dimension ref="A1:B1271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13130,6 +13130,16 @@
         <v>52.17</v>
       </c>
     </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B1271" t="n">
+        <v>52.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1274"/>
+  <dimension ref="A1:B1275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13170,6 +13170,16 @@
         <v>52.45</v>
       </c>
     </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B1275" t="n">
+        <v>52.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1275"/>
+  <dimension ref="A1:B1276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13180,6 +13180,16 @@
         <v>52.63</v>
       </c>
     </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B1276" t="n">
+        <v>52.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1277"/>
+  <dimension ref="A1:B1278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13200,6 +13200,16 @@
         <v>52.84</v>
       </c>
     </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B1278" t="n">
+        <v>52.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1279"/>
+  <dimension ref="A1:B1280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13220,6 +13220,16 @@
         <v>52.87</v>
       </c>
     </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B1280" t="n">
+        <v>52.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1281"/>
+  <dimension ref="A1:B1282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13228,6 +13228,16 @@
         <v>52.81</v>
       </c>
     </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B1282" t="n">
+        <v>52.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1282"/>
+  <dimension ref="A1:B1283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13238,6 +13238,16 @@
         <v>52.26</v>
       </c>
     </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B1283" t="n">
+        <v>52.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1283"/>
+  <dimension ref="A1:B1284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13248,6 +13248,16 @@
         <v>52.42</v>
       </c>
     </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B1284" t="n">
+        <v>52.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1285"/>
+  <dimension ref="A1:B1286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13268,6 +13268,16 @@
         <v>52.48</v>
       </c>
     </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B1286" t="n">
+        <v>52.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1286"/>
+  <dimension ref="A1:B1287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13278,6 +13278,16 @@
         <v>52.4</v>
       </c>
     </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B1287" t="n">
+        <v>52.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1287"/>
+  <dimension ref="A1:B1288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13288,6 +13288,16 @@
         <v>52.32</v>
       </c>
     </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B1288" t="n">
+        <v>52.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1288"/>
+  <dimension ref="A1:B1289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13298,6 +13298,16 @@
         <v>52.28</v>
       </c>
     </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B1289" t="n">
+        <v>52.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1290"/>
+  <dimension ref="A1:B1291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13318,6 +13318,16 @@
         <v>52.18</v>
       </c>
     </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B1291" t="n">
+        <v>52.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1292"/>
+  <dimension ref="A1:B1293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13338,6 +13338,16 @@
         <v>52.04</v>
       </c>
     </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B1293" t="n">
+        <v>51.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1294"/>
+  <dimension ref="A1:B1295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13358,6 +13358,16 @@
         <v>52.1</v>
       </c>
     </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B1295" t="n">
+        <v>52.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1295"/>
+  <dimension ref="A1:B1296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13368,6 +13368,16 @@
         <v>52.14</v>
       </c>
     </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B1296" t="n">
+        <v>52.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1296"/>
+  <dimension ref="A1:B1297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13378,6 +13378,16 @@
         <v>52.24</v>
       </c>
     </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B1297" t="n">
+        <v>52.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1297"/>
+  <dimension ref="A1:B1298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13388,6 +13388,16 @@
         <v>52.23</v>
       </c>
     </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B1298" t="n">
+        <v>51.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1299"/>
+  <dimension ref="A1:B1300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13408,6 +13408,16 @@
         <v>52.11</v>
       </c>
     </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B1300" t="n">
+        <v>52.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1300"/>
+  <dimension ref="A1:B1301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13418,6 +13418,16 @@
         <v>52.11</v>
       </c>
     </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B1301" t="n">
+        <v>52.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1301"/>
+  <dimension ref="A1:B1302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13428,6 +13428,16 @@
         <v>52.22</v>
       </c>
     </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B1302" t="n">
+        <v>52.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1302"/>
+  <dimension ref="A1:B1303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13438,6 +13438,16 @@
         <v>52.36</v>
       </c>
     </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B1303" t="n">
+        <v>52.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1303"/>
+  <dimension ref="A1:B1304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13448,6 +13448,16 @@
         <v>52.36</v>
       </c>
     </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B1304" t="n">
+        <v>52.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1304"/>
+  <dimension ref="A1:B1305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13458,6 +13458,16 @@
         <v>52.47</v>
       </c>
     </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B1305" t="n">
+        <v>52.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1305"/>
+  <dimension ref="A1:B1306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13468,6 +13468,16 @@
         <v>52.14</v>
       </c>
     </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B1306" t="n">
+        <v>52.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1306"/>
+  <dimension ref="A1:B1307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13478,6 +13478,16 @@
         <v>52.32</v>
       </c>
     </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B1307" t="n">
+        <v>52.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1307"/>
+  <dimension ref="A1:B1308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13488,6 +13488,16 @@
         <v>52.46</v>
       </c>
     </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B1308" t="n">
+        <v>52.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1309"/>
+  <dimension ref="A1:B1310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13508,6 +13508,16 @@
         <v>52.47</v>
       </c>
     </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B1310" t="n">
+        <v>52.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1310"/>
+  <dimension ref="A1:B1311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13518,6 +13518,16 @@
         <v>52.44</v>
       </c>
     </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B1311" t="n">
+        <v>52.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1311"/>
+  <dimension ref="A1:B1312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13528,6 +13528,16 @@
         <v>52.21</v>
       </c>
     </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B1312" t="n">
+        <v>52.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1312"/>
+  <dimension ref="A1:B1313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13538,6 +13538,16 @@
         <v>52.34</v>
       </c>
     </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B1313" t="n">
+        <v>52.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1636"/>
+  <dimension ref="A1:B1637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16778,6 +16778,16 @@
         <v>121.66</v>
       </c>
     </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B1637" t="n">
+        <v>121.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1315"/>
+  <dimension ref="A1:B1316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13568,6 +13568,16 @@
         <v>51.64</v>
       </c>
     </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B1316" t="n">
+        <v>51.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1317"/>
+  <dimension ref="A1:B1318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13588,6 +13588,16 @@
         <v>51.44</v>
       </c>
     </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B1318" t="n">
+        <v>51.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1318"/>
+  <dimension ref="A1:B1319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13598,6 +13598,16 @@
         <v>51.53</v>
       </c>
     </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B1319" t="n">
+        <v>51.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1319"/>
+  <dimension ref="A1:B1320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13608,6 +13608,16 @@
         <v>51.26</v>
       </c>
     </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B1320" t="n">
+        <v>51.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1320"/>
+  <dimension ref="A1:B1321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13618,6 +13618,16 @@
         <v>51.01</v>
       </c>
     </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B1321" t="n">
+        <v>50.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1321"/>
+  <dimension ref="A1:B1322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13628,6 +13628,16 @@
         <v>50.51</v>
       </c>
     </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B1322" t="n">
+        <v>50.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1322"/>
+  <dimension ref="A1:B1323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13638,6 +13638,16 @@
         <v>50.68</v>
       </c>
     </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B1323" t="n">
+        <v>50.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1323"/>
+  <dimension ref="A1:B1324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13648,6 +13648,16 @@
         <v>50.54</v>
       </c>
     </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1324" t="n">
+        <v>50.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fund_history.xlsx
+++ b/fund_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1324"/>
+  <dimension ref="A1:B1325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13658,6 +13658,16 @@
         <v>50.83</v>
       </c>
     </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1325" t="n">
+        <v>50.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
